--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -28,15 +28,15 @@
     <t>함정 최대 스폰수</t>
   </si>
   <si>
+    <t>도구 최대 스폰수</t>
+  </si>
+  <si>
+    <t>수집용 오브젝트 최대 스폰수</t>
+  </si>
+  <si>
     <t>탈출 구역 수</t>
   </si>
   <si>
-    <t>등장 적 목록</t>
-  </si>
-  <si>
-    <t>// 맵 크기를 스테이지별로 다르게 할지</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -46,6 +46,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>string[]</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -55,16 +58,22 @@
     <t>TimeLimit</t>
   </si>
   <si>
+    <t>MaxContainer</t>
+  </si>
+  <si>
+    <t>MaxTrap</t>
+  </si>
+  <si>
+    <t>MaxTool</t>
+  </si>
+  <si>
     <t>MaxObject</t>
   </si>
   <si>
-    <t>MaxTrap</t>
-  </si>
-  <si>
     <t>ExitCount</t>
   </si>
   <si>
-    <t>EnemyId</t>
+    <t>TileAddress</t>
   </si>
   <si>
     <t>Stage_01</t>
@@ -73,7 +82,7 @@
     <t>TestMap</t>
   </si>
   <si>
-    <t>Enemy_Police</t>
+    <t>All Direction Corridor,Vertical Corridor,RightTop Corridor,RightDown Corridor,LeftTop Corridor,LeftDown Corridor,Horizontal Corridor,T Corridor1,T Corridor2,T Corridor3,T Corridor4,Room1,Demo Room1,Demo Room2,Demo Room3,Demo Room4,Demo Room5,Demo Room6,Demo Room7</t>
   </si>
   <si>
     <t>Stage_02</t>
@@ -82,23 +91,17 @@
     <t>City</t>
   </si>
   <si>
-    <t>Enemy_Dog</t>
-  </si>
-  <si>
     <t>Stage_03</t>
   </si>
   <si>
     <t>Museum</t>
-  </si>
-  <si>
-    <t>Enemy_Police,Enemy_Dog</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -109,6 +112,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,12 +133,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -352,9 +363,7 @@
     <col customWidth="1" min="3" max="3" width="15.38"/>
     <col customWidth="1" min="4" max="4" width="16.75"/>
     <col customWidth="1" min="5" max="5" width="16.5"/>
-    <col customWidth="1" min="6" max="6" width="16.25"/>
-    <col customWidth="1" min="7" max="7" width="23.75"/>
-    <col customWidth="1" min="8" max="8" width="29.63"/>
+    <col customWidth="1" min="6" max="8" width="16.25"/>
     <col customWidth="1" min="9" max="9" width="17.25"/>
   </cols>
   <sheetData>
@@ -406,36 +415,48 @@
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1">
         <v>120.0</v>
@@ -449,16 +470,22 @@
       <c r="F4" s="1">
         <v>2.0</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
+      <c r="G4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1">
         <v>120.0</v>
@@ -470,18 +497,21 @@
         <v>8.0</v>
       </c>
       <c r="F5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H5" s="1">
         <v>3.0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1">
         <v>120.0</v>
@@ -493,11 +523,35 @@
         <v>10.0</v>
       </c>
       <c r="F6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H6" s="1">
         <v>3.0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>26</v>
-      </c>
+    </row>
+    <row r="13">
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="22">
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="I24" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -22,18 +22,24 @@
     <t>스테이지 제한시간</t>
   </si>
   <si>
-    <t>오브젝트 최대 스폰수</t>
+    <t>도구 스폰 수</t>
+  </si>
+  <si>
+    <t>보석 스폰 수</t>
+  </si>
+  <si>
+    <t>잡템 스폰 수</t>
+  </si>
+  <si>
+    <t>석상 스폰 수</t>
+  </si>
+  <si>
+    <t>컨테이너 오브젝트 스폰수</t>
   </si>
   <si>
     <t>함정 최대 스폰수</t>
   </si>
   <si>
-    <t>도구 최대 스폰수</t>
-  </si>
-  <si>
-    <t>수집용 오브젝트 최대 스폰수</t>
-  </si>
-  <si>
     <t>탈출 구역 수</t>
   </si>
   <si>
@@ -58,16 +64,25 @@
     <t>TimeLimit</t>
   </si>
   <si>
+    <t>MaxTool</t>
+  </si>
+  <si>
+    <t>MaxJewel</t>
+  </si>
+  <si>
+    <t>MaxJunk</t>
+  </si>
+  <si>
+    <t>MaxStatue</t>
+  </si>
+  <si>
     <t>MaxContainer</t>
   </si>
   <si>
     <t>MaxTrap</t>
   </si>
   <si>
-    <t>MaxTool</t>
-  </si>
-  <si>
-    <t>MaxObject</t>
+    <t>MaxPainting</t>
   </si>
   <si>
     <t>ExitCount</t>
@@ -361,10 +376,10 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="15.38"/>
-    <col customWidth="1" min="4" max="4" width="16.75"/>
-    <col customWidth="1" min="5" max="5" width="16.5"/>
-    <col customWidth="1" min="6" max="8" width="16.25"/>
-    <col customWidth="1" min="9" max="9" width="17.25"/>
+    <col customWidth="1" min="4" max="8" width="16.75"/>
+    <col customWidth="1" min="9" max="9" width="16.5"/>
+    <col customWidth="1" min="10" max="11" width="16.25"/>
+    <col customWidth="1" min="12" max="12" width="17.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -392,166 +407,218 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
         <v>120.0</v>
       </c>
       <c r="D4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H4" s="1">
         <v>12.0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="I4" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="J4" s="1">
         <v>6.0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="K4" s="1">
         <v>2.0</v>
       </c>
-      <c r="G4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>23</v>
+      <c r="L4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
         <v>120.0</v>
       </c>
       <c r="D5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H5" s="1">
         <v>12.0</v>
       </c>
-      <c r="E5" s="1">
+      <c r="I5" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="J5" s="1">
         <v>8.0</v>
       </c>
-      <c r="F5" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="K5" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1">
         <v>120.0</v>
       </c>
       <c r="D6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H6" s="1">
         <v>15.0</v>
       </c>
-      <c r="E6" s="1">
+      <c r="I6" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J6" s="1">
         <v>10.0</v>
       </c>
-      <c r="F6" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="K6" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="I13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14">
-      <c r="I14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15">
-      <c r="I15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16">
-      <c r="I16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="22">
-      <c r="I22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23">
-      <c r="I23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24">
-      <c r="I24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -22,18 +22,24 @@
     <t>스테이지 제한시간</t>
   </si>
   <si>
-    <t>오브젝트 최대 스폰수</t>
+    <t>도구 스폰 수</t>
+  </si>
+  <si>
+    <t>보석 스폰 수</t>
+  </si>
+  <si>
+    <t>잡템 스폰 수</t>
+  </si>
+  <si>
+    <t>석상 스폰 수</t>
+  </si>
+  <si>
+    <t>컨테이너 오브젝트 스폰수</t>
   </si>
   <si>
     <t>함정 최대 스폰수</t>
   </si>
   <si>
-    <t>도구 최대 스폰수</t>
-  </si>
-  <si>
-    <t>수집용 오브젝트 최대 스폰수</t>
-  </si>
-  <si>
     <t>탈출 구역 수</t>
   </si>
   <si>
@@ -58,16 +64,22 @@
     <t>TimeLimit</t>
   </si>
   <si>
+    <t>MaxTool</t>
+  </si>
+  <si>
+    <t>MaxJewel</t>
+  </si>
+  <si>
+    <t>MaxJunk</t>
+  </si>
+  <si>
+    <t>MaxStatue</t>
+  </si>
+  <si>
     <t>MaxContainer</t>
   </si>
   <si>
     <t>MaxTrap</t>
-  </si>
-  <si>
-    <t>MaxTool</t>
-  </si>
-  <si>
-    <t>MaxObject</t>
   </si>
   <si>
     <t>ExitCount</t>
@@ -361,10 +373,10 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="15.38"/>
-    <col customWidth="1" min="4" max="4" width="16.75"/>
-    <col customWidth="1" min="5" max="5" width="16.5"/>
-    <col customWidth="1" min="6" max="8" width="16.25"/>
-    <col customWidth="1" min="9" max="9" width="17.25"/>
+    <col customWidth="1" min="4" max="8" width="16.75"/>
+    <col customWidth="1" min="9" max="9" width="16.5"/>
+    <col customWidth="1" min="10" max="10" width="16.25"/>
+    <col customWidth="1" min="11" max="11" width="17.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -392,166 +404,202 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>120.0</v>
       </c>
       <c r="D4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H4" s="1">
         <v>12.0</v>
       </c>
-      <c r="E4" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="I4" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="J4" s="1">
         <v>2.0</v>
       </c>
-      <c r="G4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>23</v>
+      <c r="K4" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
         <v>120.0</v>
       </c>
       <c r="D5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H5" s="1">
         <v>12.0</v>
       </c>
-      <c r="E5" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="J5" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1">
         <v>120.0</v>
       </c>
       <c r="D6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H6" s="1">
         <v>15.0</v>
       </c>
-      <c r="E6" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J6" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="I13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14">
-      <c r="I14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15">
-      <c r="I15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16">
-      <c r="I16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="22">
-      <c r="I22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23">
-      <c r="I23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24">
-      <c r="I24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -1,12 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -115,67 +131,915 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
-    <font>
-      <sz val="10.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -365,24 +1229,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="15.38"/>
-    <col customWidth="1" min="4" max="8" width="16.75"/>
-    <col customWidth="1" min="9" max="9" width="16.5"/>
-    <col customWidth="1" min="10" max="11" width="16.25"/>
-    <col customWidth="1" min="12" max="12" width="17.25"/>
+    <col min="3" max="3" width="15.3796296296296" customWidth="1"/>
+    <col min="4" max="8" width="16.75" customWidth="1"/>
+    <col min="9" max="9" width="16.5" customWidth="1"/>
+    <col min="10" max="11" width="16.25" customWidth="1"/>
+    <col min="12" max="12" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -415,7 +1281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customHeight="1" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -453,7 +1319,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -491,7 +1357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customHeight="1" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -499,37 +1365,37 @@
         <v>27</v>
       </c>
       <c r="C4" s="1">
-        <v>120.0</v>
+        <v>600</v>
       </c>
       <c r="D4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="J4" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customHeight="1" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -537,34 +1403,34 @@
         <v>30</v>
       </c>
       <c r="C5" s="1">
-        <v>120.0</v>
+        <v>600</v>
       </c>
       <c r="D5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="I5" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customHeight="1" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -572,55 +1438,56 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>120.0</v>
+        <v>600</v>
       </c>
       <c r="D6" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H6" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="I6" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="K6" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customHeight="1" spans="1:12">
       <c r="L13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" customHeight="1" spans="1:12">
       <c r="L14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" customHeight="1" spans="1:12">
       <c r="L15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" customHeight="1" spans="1:12">
       <c r="L16" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" customHeight="1" spans="12:12">
       <c r="L22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="12:12">
       <c r="L23" s="2"/>
     </row>
-    <row r="24">
+    <row r="24" customHeight="1" spans="12:12">
       <c r="L24" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>MaxTrap</t>
+  </si>
+  <si>
+    <t>MaxPainting</t>
   </si>
   <si>
     <t>ExitCount</t>
@@ -375,8 +378,8 @@
     <col customWidth="1" min="3" max="3" width="15.38"/>
     <col customWidth="1" min="4" max="8" width="16.75"/>
     <col customWidth="1" min="9" max="9" width="16.5"/>
-    <col customWidth="1" min="10" max="10" width="16.25"/>
-    <col customWidth="1" min="11" max="11" width="17.25"/>
+    <col customWidth="1" min="10" max="11" width="16.25"/>
+    <col customWidth="1" min="12" max="12" width="17.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -407,7 +410,8 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -443,6 +447,9 @@
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -480,13 +487,16 @@
       <c r="K3" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
         <v>120.0</v>
@@ -510,18 +520,21 @@
         <v>12.0</v>
       </c>
       <c r="J4" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="K4" s="1">
         <v>2.0</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>27</v>
+      <c r="L4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
         <v>120.0</v>
@@ -545,15 +558,18 @@
         <v>12.0</v>
       </c>
       <c r="J5" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="K5" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1">
         <v>120.0</v>
@@ -577,29 +593,32 @@
         <v>15.0</v>
       </c>
       <c r="J6" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K6" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14">
-      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15">
-      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16">
-      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="22">
-      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23">
-      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24">
-      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -76,7 +76,10 @@
     <t>MaxStatue</t>
   </si>
   <si>
-    <t>MaxContainer</t>
+    <t>MaxFloorContainer</t>
+  </si>
+  <si>
+    <t>MaxWallContainer</t>
   </si>
   <si>
     <t>MaxTrap</t>
@@ -377,9 +380,9 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="15.38"/>
     <col customWidth="1" min="4" max="8" width="16.75"/>
-    <col customWidth="1" min="9" max="9" width="16.5"/>
-    <col customWidth="1" min="10" max="11" width="16.25"/>
-    <col customWidth="1" min="12" max="12" width="17.25"/>
+    <col customWidth="1" min="9" max="10" width="16.5"/>
+    <col customWidth="1" min="11" max="12" width="16.25"/>
+    <col customWidth="1" min="13" max="13" width="17.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -407,11 +410,12 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -450,6 +454,9 @@
         <v>12</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -490,16 +497,19 @@
       <c r="L3" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1">
-        <v>120.0</v>
+        <v>600.0</v>
       </c>
       <c r="D4" s="1">
         <v>2.0</v>
@@ -514,30 +524,33 @@
         <v>2.0</v>
       </c>
       <c r="H4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J4" s="1">
         <v>12.0</v>
       </c>
-      <c r="I4" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>6.0</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>2.0</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>28</v>
+      <c r="M4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1">
-        <v>120.0</v>
+        <v>600.0</v>
       </c>
       <c r="D5" s="1">
         <v>4.0</v>
@@ -552,27 +565,30 @@
         <v>4.0</v>
       </c>
       <c r="H5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J5" s="1">
         <v>12.0</v>
       </c>
-      <c r="I5" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>8.0</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1">
-        <v>120.0</v>
+        <v>600.0</v>
       </c>
       <c r="D6" s="1">
         <v>6.0</v>
@@ -587,38 +603,41 @@
         <v>6.0</v>
       </c>
       <c r="H6" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="J6" s="1">
         <v>15.0</v>
       </c>
-      <c r="I6" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>10.0</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14">
-      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
     </row>
     <row r="15">
-      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
     </row>
     <row r="16">
-      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
     </row>
     <row r="22">
-      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
     </row>
     <row r="23">
-      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
     </row>
     <row r="24">
-      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -82,7 +82,10 @@
     <t>MaxWallContainer</t>
   </si>
   <si>
-    <t>MaxTrap</t>
+    <t>MaxFloorTrap</t>
+  </si>
+  <si>
+    <t>MaxCeilingTrap</t>
   </si>
   <si>
     <t>MaxPainting</t>
@@ -380,9 +383,9 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="15.38"/>
     <col customWidth="1" min="4" max="8" width="16.75"/>
-    <col customWidth="1" min="9" max="10" width="16.5"/>
-    <col customWidth="1" min="11" max="12" width="16.25"/>
-    <col customWidth="1" min="13" max="13" width="17.25"/>
+    <col customWidth="1" min="9" max="11" width="16.5"/>
+    <col customWidth="1" min="12" max="13" width="16.25"/>
+    <col customWidth="1" min="14" max="14" width="17.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -414,8 +417,8 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -457,6 +460,9 @@
         <v>12</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -500,13 +506,16 @@
       <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1">
         <v>600.0</v>
@@ -530,24 +539,27 @@
         <v>3.0</v>
       </c>
       <c r="J4" s="1">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="K4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="L4" s="1">
         <v>6.0</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>2.0</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>29</v>
+      <c r="N4" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1">
         <v>600.0</v>
@@ -571,21 +583,24 @@
         <v>5.0</v>
       </c>
       <c r="J5" s="1">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="K5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="L5" s="1">
         <v>8.0</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>600.0</v>
@@ -609,35 +624,38 @@
         <v>7.0</v>
       </c>
       <c r="J6" s="1">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="K6" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="L6" s="1">
         <v>10.0</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
     </row>
     <row r="14">
-      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
     </row>
     <row r="15">
-      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
     </row>
     <row r="16">
-      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
     </row>
     <row r="22">
-      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
     </row>
     <row r="23">
-      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
     </row>
     <row r="24">
-      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -1,12 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -121,67 +137,915 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
-    <font>
-      <sz val="10.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -371,24 +1235,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="15.38"/>
-    <col customWidth="1" min="4" max="8" width="16.75"/>
-    <col customWidth="1" min="9" max="11" width="16.5"/>
-    <col customWidth="1" min="12" max="13" width="16.25"/>
-    <col customWidth="1" min="14" max="14" width="17.25"/>
+    <col min="3" max="3" width="15.3796296296296" customWidth="1"/>
+    <col min="4" max="8" width="16.75" customWidth="1"/>
+    <col min="9" max="11" width="16.5" customWidth="1"/>
+    <col min="12" max="13" width="16.25" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,7 +1288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -466,7 +1332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -510,7 +1376,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customHeight="1" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -518,43 +1384,43 @@
         <v>29</v>
       </c>
       <c r="C4" s="1">
-        <v>600.0</v>
+        <v>300</v>
       </c>
       <c r="D4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K4" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="M4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customHeight="1" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -562,40 +1428,40 @@
         <v>32</v>
       </c>
       <c r="C5" s="1">
-        <v>600.0</v>
+        <v>600</v>
       </c>
       <c r="D5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I5" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="L5" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="M5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customHeight="1" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -603,61 +1469,62 @@
         <v>34</v>
       </c>
       <c r="C6" s="1">
-        <v>600.0</v>
+        <v>600</v>
       </c>
       <c r="D6" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H6" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J6" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customHeight="1" spans="1:14">
       <c r="N13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" customHeight="1" spans="1:14">
       <c r="N14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" customHeight="1" spans="1:14">
       <c r="N15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" customHeight="1" spans="1:14">
       <c r="N16" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" customHeight="1" spans="14:14">
       <c r="N22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="14:14">
       <c r="N23" s="2"/>
     </row>
-    <row r="24">
+    <row r="24" customHeight="1" spans="14:14">
       <c r="N24" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hdong\OneDrive\바탕 화면\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C34B102-579F-4002-B44C-92B455E68DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="시트1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -31,6 +22,9 @@
     <t>스테이지 제한시간</t>
   </si>
   <si>
+    <t>몬스터 스폰 수</t>
+  </si>
+  <si>
     <t>보석 스폰 수</t>
   </si>
   <si>
@@ -70,6 +64,9 @@
     <t>TimeLimit</t>
   </si>
   <si>
+    <t>StageEnemyId</t>
+  </si>
+  <si>
     <t>MaxJewel</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
     <t>TestMap</t>
   </si>
   <si>
+    <t>StageEnemy_01</t>
+  </si>
+  <si>
     <t>All Direction Corridor,Vertical Corridor,RightTop Corridor,RightDown Corridor,LeftTop Corridor,LeftDown Corridor,Horizontal Corridor,T Corridor1,T Corridor2,T Corridor3,T Corridor4,Room1,Demo Room1,Demo Room2,Demo Room3,Demo Room4,Demo Room5,Demo Room6,Demo Room7</t>
   </si>
   <si>
@@ -115,76 +115,38 @@
     <t>City</t>
   </si>
   <si>
+    <t>StageEnemy_02</t>
+  </si>
+  <si>
     <t>Stage_03</t>
   </si>
   <si>
     <t>Museum</t>
   </si>
   <si>
-    <t>몬스터 스폰 수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StageEnemyId</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage_Enemy_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage_Enemy_02</t>
-  </si>
-  <si>
-    <t>Stage_Enemy_03</t>
+    <t>StageEnemy_03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -192,43 +154,38 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+  <cellXfs count="4">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -236,7 +193,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -426,27 +383,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="11" width="16.44140625" customWidth="1"/>
-    <col min="12" max="13" width="16.21875" customWidth="1"/>
-    <col min="14" max="14" width="17.21875" customWidth="1"/>
+    <col customWidth="1" min="3" max="3" width="15.38"/>
+    <col customWidth="1" min="4" max="8" width="16.75"/>
+    <col customWidth="1" min="9" max="11" width="16.5"/>
+    <col customWidth="1" min="12" max="13" width="16.25"/>
+    <col customWidth="1" min="14" max="14" width="17.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,267 +410,266 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>33</v>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="13.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="13.2">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="13.2">
-      <c r="A4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="1">
-        <v>300</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1">
-        <v>6</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2</v>
-      </c>
-      <c r="H4" s="1">
-        <v>4</v>
-      </c>
-      <c r="I4" s="1">
-        <v>3</v>
-      </c>
-      <c r="J4" s="1">
-        <v>8</v>
-      </c>
-      <c r="K4" s="1">
-        <v>4</v>
-      </c>
-      <c r="L4" s="1">
-        <v>6</v>
-      </c>
-      <c r="M4" s="1">
-        <v>2</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="13.2">
-      <c r="A5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="1">
-        <v>600</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C6" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="1">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1">
-        <v>4</v>
-      </c>
-      <c r="H5" s="1">
-        <v>6</v>
-      </c>
-      <c r="I5" s="1">
-        <v>5</v>
-      </c>
-      <c r="J5" s="1">
-        <v>10</v>
-      </c>
-      <c r="K5" s="1">
-        <v>6</v>
-      </c>
-      <c r="L5" s="1">
-        <v>8</v>
-      </c>
-      <c r="M5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="13.2">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="1">
-        <v>600</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="E6" s="1">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="F6" s="1">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="G6" s="1">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="H6" s="1">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="I6" s="1">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="J6" s="1">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="K6" s="1">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="L6" s="1">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="M6" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="15.75" customHeight="1">
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" ht="15.75" customHeight="1">
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1">
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1">
-      <c r="N16" s="2"/>
-    </row>
-    <row r="22" spans="14:14" ht="15.75" customHeight="1">
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="14:14" ht="15.75" customHeight="1">
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="14:14" ht="15.75" customHeight="1">
-      <c r="N24" s="2"/>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="22">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24">
+      <c r="N24" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>